--- a/game-stats/Week7_LOB_vs_All-Madden_game2.xlsx
+++ b/game-stats/Week7_LOB_vs_All-Madden_game2.xlsx
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>No Name</t>
+          <t>Charles II</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
